--- a/EXCEL/Data/arbejdstidfordeling/fysioterapeuter.xlsx
+++ b/EXCEL/Data/arbejdstidfordeling/fysioterapeuter.xlsx
@@ -133,7 +133,7 @@
     <t>Datasæt 00 2023</t>
   </si>
   <si>
-    <t>Kørsel 10.4.2026 13.31.28</t>
+    <t>Kørsel 14.4.2026 12.26.19</t>
   </si>
   <si>
     <t/>
